--- a/lojas-proprias/pwr_reports/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-08-24 - 2026-08-30).xlsx
+++ b/lojas-proprias/pwr_reports/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-08-24 - 2026-08-30).xlsx
@@ -236,7 +236,7 @@
     <t>559.8</t>
   </si>
   <si>
-    <t>371.3</t>
+    <t>379.8</t>
   </si>
   <si>
     <t>5.68</t>
@@ -251,10 +251,10 @@
     <t>6.5</t>
   </si>
   <si>
-    <t>51.5%</t>
-  </si>
-  <si>
-    <t>13.8%</t>
+    <t>50.3%</t>
+  </si>
+  <si>
+    <t>14.0%</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -278,10 +278,13 @@
     <t>3.0%</t>
   </si>
   <si>
-    <t>1284.0</t>
-  </si>
-  <si>
-    <t>1076.0</t>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>1328.0</t>
+  </si>
+  <si>
+    <t>1118.0</t>
   </si>
   <si>
     <t>53.0</t>
@@ -290,7 +293,7 @@
     <t>9.0</t>
   </si>
   <si>
-    <t>146.0</t>
+    <t>152.0</t>
   </si>
   <si>
     <t>70.0</t>
@@ -299,13 +302,13 @@
     <t>13.0</t>
   </si>
   <si>
-    <t>419.0</t>
-  </si>
-  <si>
-    <t>235.0</t>
-  </si>
-  <si>
-    <t>236.0</t>
+    <t>427.0</t>
+  </si>
+  <si>
+    <t>239.0</t>
+  </si>
+  <si>
+    <t>262.0</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -2370,7 +2373,7 @@
         <v>1298</v>
       </c>
       <c r="O11" s="6">
-        <v>586</v>
+        <v>764</v>
       </c>
       <c r="P11" s="7">
         <v>6.8267902627511585</v>
@@ -2388,37 +2391,37 @@
         <v>0.37565445026178013</v>
       </c>
       <c r="U11" s="9">
-        <v>0.13822525597269625</v>
+        <v>0.16099476439790575</v>
       </c>
       <c r="V11" s="9">
-        <v>0.0017064846416382253</v>
+        <v>0.0013089005235602095</v>
       </c>
       <c r="W11" s="9">
-        <v>0.0017064846409999999</v>
+        <v>0.0013089005230000001</v>
       </c>
       <c r="X11" s="9">
-        <v>0.020477815699658702</v>
+        <v>0.02356020942408377</v>
       </c>
       <c r="Y11" s="9">
         <v>0</v>
       </c>
       <c r="Z11" s="9">
-        <v>0.0017064846416382253</v>
+        <v>0.0013089005235602095</v>
       </c>
       <c r="AA11" s="9">
-        <v>0.023890784982935155</v>
+        <v>0.028795811518324606</v>
       </c>
       <c r="AB11" s="9">
-        <v>0.017064846416382253</v>
+        <v>0.01832460732984293</v>
       </c>
       <c r="AC11" s="9">
-        <v>0.08191126279863481</v>
+        <v>0.096858638743455502</v>
       </c>
       <c r="AD11" s="6">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="AE11" s="6">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="AF11" s="6">
         <v>1</v>
@@ -2427,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="AH11" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AI11" s="6">
         <v>0</v>
@@ -2436,13 +2439,13 @@
         <v>1</v>
       </c>
       <c r="AK11" s="6">
+        <v>22</v>
+      </c>
+      <c r="AL11" s="6">
         <v>14</v>
       </c>
-      <c r="AL11" s="6">
-        <v>10</v>
-      </c>
       <c r="AM11" s="6">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -4355,43 +4358,43 @@
         <v>88</v>
       </c>
       <c t="s" r="AC24" s="11">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="AD24" s="11">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="AE24" s="11">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="AF24" s="11">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="AG24" s="11">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="AH24" s="11">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="AI24" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="AJ24" s="11">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="AK24" s="11">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="AL24" s="11">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="AM24" s="11">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="AN24" s="11">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="AO24" s="11">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AP24" s="12"/>
       <c t="s" r="AQ24" s="12">
@@ -4408,10 +4411,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX24" s="11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="AY24" s="11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AZ24" s="12"/>
       <c r="BA24" s="12"/>
